--- a/data/trans_camb/IP11-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP11-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 4,59</t>
+          <t>-5,2; 4,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 5,87</t>
+          <t>-5,45; 5,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 1,91</t>
+          <t>-7,72; 1,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,05; 19,2</t>
+          <t>4,57; 18,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 4,8</t>
+          <t>-3,86; 5,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 6,03</t>
+          <t>-4,97; 5,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 10,3</t>
+          <t>1,07; 10,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 3,73</t>
+          <t>-3,14; 3,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 2,06</t>
+          <t>-4,99; 2,08</t>
         </is>
       </c>
     </row>
@@ -783,27 +783,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-75,73; 270,61</t>
+          <t>-76,69; 287,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-80,95; 403,31</t>
+          <t>-82,53; 256,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 254,19</t>
+          <t>-100,0; 132,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47,06; 1449,77</t>
+          <t>53,59; 1658,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-90,6; 472,35</t>
+          <t>-84,53; 615,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,12; 447,0</t>
+          <t>12,0; 431,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,94; 162,51</t>
+          <t>-59,72; 182,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-90,38; 158,57</t>
+          <t>-91,39; 135,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 5,93</t>
+          <t>0,37; 6,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,5</t>
+          <t>-4,05; 0,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,88; -0,6</t>
+          <t>-4,8; -0,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 4,08</t>
+          <t>-1,13; 4,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 1,22</t>
+          <t>-3,93; 1,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,37; -2,59</t>
+          <t>-7,14; -2,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 4,26</t>
+          <t>0,28; 4,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 0,34</t>
+          <t>-3,08; 0,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,43; -2,23</t>
+          <t>-5,52; -2,41</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,82; 153,57</t>
+          <t>5,02; 158,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,2; 13,08</t>
+          <t>-60,87; 15,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-76,06; -11,23</t>
+          <t>-76,31; -15,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,04; 64,79</t>
+          <t>-14,92; 70,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,71; 19,89</t>
+          <t>-42,02; 24,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,5; -40,44</t>
+          <t>-79,43; -40,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 76,07</t>
+          <t>2,24; 76,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,54; 6,88</t>
+          <t>-40,89; 3,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-72,85; -39,33</t>
+          <t>-72,57; -40,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 4,26</t>
+          <t>-4,04; 4,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,74; -0,16</t>
+          <t>-6,98; -0,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 1,62</t>
+          <t>-6,52; 1,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,91</t>
+          <t>0,57; 9,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 2,79</t>
+          <t>-4,51; 2,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 4,21</t>
+          <t>-3,52; 3,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 5,83</t>
+          <t>-0,34; 5,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 0,69</t>
+          <t>-4,48; 0,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 1,55</t>
+          <t>-3,98; 2,09</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,62; 107,65</t>
+          <t>-50,84; 118,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-83,38; 4,84</t>
+          <t>-84,99; 6,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-75,77; 53,25</t>
+          <t>-78,95; 46,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,69; 414,38</t>
+          <t>6,88; 382,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,49; 125,54</t>
+          <t>-70,43; 120,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-63,92; 190,9</t>
+          <t>-61,01; 167,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 147,28</t>
+          <t>-6,26; 146,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,59; 24,72</t>
+          <t>-68,08; 19,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,27; 45,72</t>
+          <t>-60,56; 56,51</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 4,07</t>
+          <t>0,04; 4,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -0,17</t>
+          <t>-3,55; -0,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,4; -0,95</t>
+          <t>-4,38; -0,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,58</t>
+          <t>0,84; 5,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,9</t>
+          <t>-2,99; 1,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,34; -1,39</t>
+          <t>-5,15; -1,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,24</t>
+          <t>1,23; 4,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,75; -0,13</t>
+          <t>-2,58; -0,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; -1,6</t>
+          <t>-4,16; -1,71</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 95,65</t>
+          <t>0,4; 96,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-60,67; -3,57</t>
+          <t>-57,75; 0,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,97; -21,1</t>
+          <t>-70,19; -18,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,61; 101,63</t>
+          <t>10,71; 104,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,37; 16,98</t>
+          <t>-40,03; 21,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,93; -25,11</t>
+          <t>-69,6; -26,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,29; 82,03</t>
+          <t>18,85; 84,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-41,93; -2,71</t>
+          <t>-40,89; -3,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-64,67; -31,12</t>
+          <t>-64,05; -33,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP11-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP11-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 4,65</t>
+          <t>-5,85; 4,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 5,13</t>
+          <t>-5,29; 5,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 1,42</t>
+          <t>-7,33; 2,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 18,71</t>
+          <t>4,75; 19,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 5,38</t>
+          <t>-3,99; 5,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 5,91</t>
+          <t>-4,82; 4,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 10,11</t>
+          <t>1,42; 10,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,95</t>
+          <t>-3,45; 3,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 2,08</t>
+          <t>-4,74; 2,23</t>
         </is>
       </c>
     </row>
@@ -783,27 +783,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-76,69; 287,42</t>
+          <t>-78,07; 182,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-82,53; 256,6</t>
+          <t>-83,95; 324,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 132,36</t>
+          <t>-100,0; 179,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53,59; 1658,97</t>
+          <t>55,17; 1592,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-84,53; 615,32</t>
+          <t>-100,0; 395,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,0; 431,91</t>
+          <t>21,32; 541,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,72; 182,1</t>
+          <t>-67,36; 169,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-91,39; 135,72</t>
+          <t>-90,83; 141,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 6,01</t>
+          <t>0,81; 6,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,55</t>
+          <t>-3,73; 0,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,8; -0,63</t>
+          <t>-4,73; -0,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 4,48</t>
+          <t>-1,32; 4,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 1,44</t>
+          <t>-3,76; 1,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -2,71</t>
+          <t>-7,14; -2,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 4,44</t>
+          <t>0,43; 4,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,18</t>
+          <t>-3,31; 0,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,52; -2,41</t>
+          <t>-5,49; -2,26</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-52,65%</t>
+          <t>-52,57%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-59,31%</t>
+          <t>-59,28%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 158,16</t>
+          <t>10,12; 157,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,87; 15,19</t>
+          <t>-59,08; 17,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-76,31; -15,32</t>
+          <t>-74,56; -17,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,92; 70,64</t>
+          <t>-14,64; 69,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,02; 24,59</t>
+          <t>-42,12; 26,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,43; -40,57</t>
+          <t>-78,48; -38,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 76,5</t>
+          <t>5,42; 78,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,89; 3,82</t>
+          <t>-43,59; 8,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-72,57; -40,58</t>
+          <t>-73,74; -39,52</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 4,21</t>
+          <t>-4,03; 4,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,98; -0,08</t>
+          <t>-6,73; 0,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 1,11</t>
+          <t>-5,91; 1,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 9,57</t>
+          <t>0,23; 9,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 2,47</t>
+          <t>-3,92; 2,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 3,96</t>
+          <t>-3,82; 3,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 5,42</t>
+          <t>-0,64; 5,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 0,5</t>
+          <t>-4,53; 0,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 2,09</t>
+          <t>-4,04; 1,49</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-50,84; 118,21</t>
+          <t>-52,06; 114,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-84,99; 6,23</t>
+          <t>-83,21; 8,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-78,95; 46,05</t>
+          <t>-78,21; 61,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,88; 382,13</t>
+          <t>-4,4; 396,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,43; 120,06</t>
+          <t>-66,13; 113,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,01; 167,31</t>
+          <t>-64,27; 160,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 146,41</t>
+          <t>-11,76; 151,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,08; 19,6</t>
+          <t>-68,39; 12,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-60,56; 56,51</t>
+          <t>-62,06; 42,46</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,16</t>
+          <t>0,04; 4,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; -0,04</t>
+          <t>-3,59; -0,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,38; -0,83</t>
+          <t>-4,48; -0,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,62</t>
+          <t>1,07; 5,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,13</t>
+          <t>-3,06; 1,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,15; -1,54</t>
+          <t>-5,23; -1,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,42</t>
+          <t>1,16; 4,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,58; -0,18</t>
+          <t>-2,88; -0,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,16; -1,71</t>
+          <t>-4,22; -1,67</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-50,2%</t>
+          <t>-50,14%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-50,45%</t>
+          <t>-50,43%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 96,79</t>
+          <t>0,09; 101,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,75; 0,56</t>
+          <t>-57,18; 1,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,19; -18,09</t>
+          <t>-70,72; -21,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,71; 104,22</t>
+          <t>13,85; 102,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,03; 21,6</t>
+          <t>-40,41; 19,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,6; -26,01</t>
+          <t>-68,35; -24,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,85; 84,64</t>
+          <t>16,99; 81,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,89; -3,25</t>
+          <t>-44,08; -1,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-64,05; -33,19</t>
+          <t>-63,81; -31,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP11-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP11-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,42</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,26</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,14</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,39</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,55</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,33</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,42</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,09</t>
+          <t>-2,12</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,83</t>
+          <t>-1,72</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 4,14</t>
+          <t>5,05; 19,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 5,3</t>
+          <t>-4,64; 4,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 2,07</t>
+          <t>-5,15; 5,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 19,14</t>
+          <t>-5,16; 4,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 5,08</t>
+          <t>-5,39; 5,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 4,96</t>
+          <t>-6,7; 3,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 10,45</t>
+          <t>1,27; 10,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 3,67</t>
+          <t>-3,29; 3,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 2,23</t>
+          <t>-4,73; 2,19</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>346,57%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12,73%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-38,51%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-3,1%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-8,61%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-56,3%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>346,57%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>12,73%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-33,42%</t>
+          <t>-46,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-46,74%</t>
+          <t>-44,05%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-78,07; 182,04</t>
+          <t>47,06; 1449,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-83,95; 324,0</t>
+          <t>-90,6; 472,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 179,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55,17; 1592,75</t>
+          <t>-75,73; 270,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 395,25</t>
+          <t>-80,95; 403,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 404,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,32; 541,19</t>
+          <t>16,12; 447,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-67,36; 169,91</t>
+          <t>-65,94; 162,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-90,83; 141,0</t>
+          <t>-91,42; 153,48</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,37</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,31</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-4,85</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,34</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-1,56</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,66</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,37</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,31</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,88</t>
+          <t>-2,51</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,85</t>
+          <t>-3,76</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 6,32</t>
+          <t>-1,64; 4,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,58</t>
+          <t>-3,89; 1,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,73; -0,78</t>
+          <t>-7,35; -2,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 4,31</t>
+          <t>0,35; 5,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 1,56</t>
+          <t>-3,76; 0,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,14; -2,64</t>
+          <t>-4,64; -0,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,37</t>
+          <t>0,22; 4,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,43</t>
+          <t>-3,22; 0,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,49; -2,26</t>
+          <t>-5,38; -2,18</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17,7%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-16,91%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-62,64%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>66,07%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-30,84%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-52,57%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17,7%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-16,91%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-63,05%</t>
+          <t>-49,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-59,28%</t>
+          <t>-57,96%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,12; 157,49</t>
+          <t>-18,04; 64,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,08; 17,21</t>
+          <t>-42,71; 19,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-74,56; -17,0</t>
+          <t>-79,33; -39,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 69,58</t>
+          <t>4,82; 153,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,12; 26,13</t>
+          <t>-60,2; 13,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,48; -38,0</t>
+          <t>-74,44; -8,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 78,3</t>
+          <t>2,91; 76,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,59; 8,48</t>
+          <t>-43,54; 6,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-73,74; -39,52</t>
+          <t>-71,83; -38,13</t>
         </is>
       </c>
     </row>
@@ -1056,34 +1056,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,99</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,63</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,11</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-0,01</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-3,25</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>-2,45</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,99</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,63</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>2,48</t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,19</t>
+          <t>-1,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 4,16</t>
+          <t>1,01; 9,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 0,1</t>
+          <t>-4,59; 2,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 1,57</t>
+          <t>-3,47; 4,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 9,28</t>
+          <t>-4,19; 4,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 2,67</t>
+          <t>-6,74; -0,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 3,8</t>
+          <t>-6,09; 1,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 5,88</t>
+          <t>-0,55; 5,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 0,34</t>
+          <t>-4,43; 0,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 1,49</t>
+          <t>-3,91; 1,56</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>116,75%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-14,84%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-0,13%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-55,72%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-42,05%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>116,75%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-14,84%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>-42,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-23,34%</t>
+          <t>-23,18%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,06; 114,72</t>
+          <t>8,69; 414,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-83,21; 8,58</t>
+          <t>-70,49; 125,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-78,21; 61,53</t>
+          <t>-63,87; 197,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 396,11</t>
+          <t>-52,62; 107,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,13; 113,74</t>
+          <t>-83,38; 4,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,27; 160,86</t>
+          <t>-77,43; 55,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 151,6</t>
+          <t>-10,48; 147,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,39; 12,46</t>
+          <t>-68,59; 24,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,06; 42,46</t>
+          <t>-61,85; 48,01</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,97</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-3,26</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,09</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-1,86</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-2,6</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,33</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,97</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,29</t>
+          <t>-2,45</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,94</t>
+          <t>-2,86</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,37</t>
+          <t>1,07; 5,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -0,04</t>
+          <t>-3,09; 0,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,48; -0,98</t>
+          <t>-5,38; -1,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,63</t>
+          <t>-0,05; 4,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,04</t>
+          <t>-3,79; -0,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,23; -1,41</t>
+          <t>-4,13; -0,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,36</t>
+          <t>1,26; 4,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,88; -0,14</t>
+          <t>-2,75; -0,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -1,67</t>
+          <t>-4,07; -1,55</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>51,73%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-15,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-50,66%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>40,31%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-35,79%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-50,14%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>51,73%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-15,0%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-50,99%</t>
+          <t>-47,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-50,43%</t>
+          <t>-49,08%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,09; 101,47</t>
+          <t>11,61; 101,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,18; 1,69</t>
+          <t>-40,37; 16,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,72; -21,84</t>
+          <t>-70,04; -24,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,85; 102,61</t>
+          <t>-1,32; 95,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,41; 19,5</t>
+          <t>-60,67; -3,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,35; -24,49</t>
+          <t>-66,99; -10,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,99; 81,67</t>
+          <t>19,29; 82,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-44,08; -1,56</t>
+          <t>-41,93; -2,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-63,81; -31,24</t>
+          <t>-63,24; -29,13</t>
         </is>
       </c>
     </row>
